--- a/warehouse_financial_system/FILE_MAU_NHAP_CHI_PHI_TAI_CHINH_KHO.xlsx
+++ b/warehouse_financial_system/FILE_MAU_NHAP_CHI_PHI_TAI_CHINH_KHO.xlsx
@@ -476,7 +476,7 @@
         <v>220000000</v>
       </c>
       <c r="C2" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="D2" t="n">
         <v>35000000</v>

--- a/warehouse_financial_system/FILE_MAU_NHAP_CHI_PHI_TAI_CHINH_KHO.xlsx
+++ b/warehouse_financial_system/FILE_MAU_NHAP_CHI_PHI_TAI_CHINH_KHO.xlsx
@@ -424,7 +424,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Quỹ Lương Nhân Sự Kho (VND)</t>
+          <t>Quỹ Lương Nhân Sự Kho Ca 12H (VND)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -473,7 +473,7 @@
         <v>180000000</v>
       </c>
       <c r="B2" t="n">
-        <v>220000000</v>
+        <v>333500000</v>
       </c>
       <c r="C2" t="n">
         <v>29</v>

--- a/warehouse_financial_system/FILE_MAU_NHAP_CHI_PHI_TAI_CHINH_KHO.xlsx
+++ b/warehouse_financial_system/FILE_MAU_NHAP_CHI_PHI_TAI_CHINH_KHO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,45 +424,60 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Quỹ Lương Nhân Sự Kho Ca 12H (VND)</t>
+          <t>Lương Quản Lý Kho (VND)</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Số Lượng Nhân Sự Kho (Người)</t>
+          <t>Số Lượng Thủ Kho (Người)</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Lương Thủ Kho (VND/Người)</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Số Lượng Nhân Viên Kho Ca 12H (Người)</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Lương Nhân Viên Kho (VND/Người)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Chi Phí Điện Nước Kho (VND)</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Chi Phí Xe Nâng &amp; Thiết Bị (VND)</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Số Lượng Xe Nâng &amp; IT Assets (Cái)</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Chi Phí Màng PE &amp; Vật Tư (VND)</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Lãi Suất Giam Vốn (%/Năm)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Tổng Giá Trị Tồn Kho Realtime (VND)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Sản Lượng Xuất Nhập (Kg/Tháng)</t>
         </is>
@@ -473,30 +488,39 @@
         <v>180000000</v>
       </c>
       <c r="B2" t="n">
-        <v>333500000</v>
+        <v>45000000</v>
       </c>
       <c r="C2" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
+        <v>20000000</v>
+      </c>
+      <c r="E2" t="n">
+        <v>25</v>
+      </c>
+      <c r="F2" t="n">
+        <v>10500000</v>
+      </c>
+      <c r="G2" t="n">
         <v>35000000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="H2" t="n">
         <v>25000000</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>22</v>
       </c>
-      <c r="G2" t="n">
+      <c r="J2" t="n">
         <v>18000000</v>
       </c>
-      <c r="H2" t="n">
+      <c r="K2" t="n">
         <v>15</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>35000000000</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>450000</v>
       </c>
     </row>

--- a/warehouse_financial_system/FILE_MAU_NHAP_CHI_PHI_TAI_CHINH_KHO.xlsx
+++ b/warehouse_financial_system/FILE_MAU_NHAP_CHI_PHI_TAI_CHINH_KHO.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:P2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,30 +454,45 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Số Lượng Pallet Nhựa Ống Sắt (Cái)</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Giá 1 Pallet Nhựa Ống Sắt (VND)</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Tỷ Lệ Hao Hụt/Bể Pallet (%/Năm)</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>Chi Phí Xe Nâng &amp; Thiết Bị (VND)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Số Lượng Xe Nâng &amp; IT Assets (Cái)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Chi Phí Màng PE &amp; Vật Tư (VND)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Lãi Suất Giam Vốn (%/Năm)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Tổng Giá Trị Tồn Kho Realtime (VND)</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sản Lượng Xuất Nhập (Kg/Tháng)</t>
         </is>
@@ -506,21 +521,30 @@
         <v>35000000</v>
       </c>
       <c r="H2" t="n">
+        <v>4038</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
         <v>25000000</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>22</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>18000000</v>
       </c>
-      <c r="K2" t="n">
+      <c r="N2" t="n">
         <v>15</v>
       </c>
-      <c r="L2" t="n">
+      <c r="O2" t="n">
         <v>35000000000</v>
       </c>
-      <c r="M2" t="n">
+      <c r="P2" t="n">
         <v>450000</v>
       </c>
     </row>
